--- a/output/roomself_excel/7587.xlsx
+++ b/output/roomself_excel/7587.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38259</v>
+        <v>123726</v>
       </c>
       <c r="D2" t="n">
-        <v>1840</v>
+        <v>2880</v>
       </c>
       <c r="E2" t="n">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="F2" t="n">
-        <v>136</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>178175</v>
+        <v>166621</v>
       </c>
       <c r="D3" t="n">
-        <v>6040</v>
+        <v>3308</v>
       </c>
       <c r="E3" t="n">
-        <v>654</v>
+        <v>497</v>
       </c>
       <c r="F3" t="n">
-        <v>142</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24840</v>
+        <v>155946</v>
       </c>
       <c r="D5" t="n">
-        <v>1276</v>
+        <v>3212</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>474</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>155946</v>
+        <v>80028</v>
       </c>
       <c r="D6" t="n">
-        <v>3212</v>
+        <v>2316</v>
       </c>
       <c r="E6" t="n">
-        <v>474</v>
+        <v>228</v>
       </c>
       <c r="F6" t="n">
         <v>27</v>
@@ -580,16 +580,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>80028</v>
+        <v>93018</v>
       </c>
       <c r="D7" t="n">
-        <v>2316</v>
+        <v>2612</v>
       </c>
       <c r="E7" t="n">
-        <v>228</v>
+        <v>525</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>108019</v>
+        <v>24840</v>
       </c>
       <c r="D8" t="n">
-        <v>4400</v>
+        <v>1276</v>
       </c>
       <c r="E8" t="n">
-        <v>1045</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23676</v>
+        <v>30960</v>
       </c>
       <c r="D9" t="n">
-        <v>1252</v>
+        <v>1408</v>
       </c>
       <c r="E9" t="n">
-        <v>195</v>
+        <v>367</v>
       </c>
       <c r="F9" t="n">
-        <v>174</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30960</v>
+        <v>17690</v>
       </c>
       <c r="D10" t="n">
-        <v>1408</v>
+        <v>1068</v>
       </c>
       <c r="E10" t="n">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>447417</v>
+        <v>22006</v>
       </c>
       <c r="D11" t="n">
-        <v>9260</v>
+        <v>1368</v>
       </c>
       <c r="E11" t="n">
-        <v>875</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>786</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>82022</v>
+        <v>15912</v>
       </c>
       <c r="D13" t="n">
-        <v>2592</v>
+        <v>1012</v>
       </c>
       <c r="E13" t="n">
-        <v>460</v>
+        <v>136</v>
       </c>
       <c r="F13" t="n">
-        <v>187</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>148512</v>
+        <v>15678</v>
       </c>
       <c r="D14" t="n">
-        <v>3268</v>
+        <v>1004</v>
       </c>
       <c r="E14" t="n">
-        <v>567</v>
+        <v>164</v>
       </c>
       <c r="F14" t="n">
-        <v>319</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17690</v>
+        <v>148512</v>
       </c>
       <c r="D15" t="n">
-        <v>1068</v>
+        <v>3268</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15912</v>
+        <v>38259</v>
       </c>
       <c r="D16" t="n">
-        <v>1012</v>
+        <v>1840</v>
       </c>
       <c r="E16" t="n">
+        <v>378</v>
+      </c>
+      <c r="F16" t="n">
         <v>136</v>
-      </c>
-      <c r="F16" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -796,20 +796,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>93018</v>
+        <v>178175</v>
       </c>
       <c r="D17" t="n">
-        <v>2612</v>
+        <v>6040</v>
       </c>
       <c r="E17" t="n">
-        <v>525</v>
+        <v>654</v>
       </c>
       <c r="F17" t="n">
-        <v>177</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18">
@@ -818,20 +818,108 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15678</v>
+        <v>108019</v>
       </c>
       <c r="D18" t="n">
-        <v>1004</v>
+        <v>4400</v>
       </c>
       <c r="E18" t="n">
-        <v>164</v>
+        <v>1045</v>
       </c>
       <c r="F18" t="n">
-        <v>142</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>23676</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1252</v>
+      </c>
+      <c r="E19" t="n">
+        <v>195</v>
+      </c>
+      <c r="F19" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>79864</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2920</v>
+      </c>
+      <c r="E20" t="n">
+        <v>200</v>
+      </c>
+      <c r="F20" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>82022</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2592</v>
+      </c>
+      <c r="E21" t="n">
+        <v>244</v>
+      </c>
+      <c r="F21" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>55200</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1896</v>
+      </c>
+      <c r="E22" t="n">
+        <v>305</v>
+      </c>
+      <c r="F22" t="n">
+        <v>220</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/7587.xlsx
+++ b/output/roomself_excel/7587.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2880</v>
       </c>
-      <c r="E2" t="n">
-        <v>357</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>249</v>
+        <v>324</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>218</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -497,11 +533,27 @@
       <c r="D3" t="n">
         <v>3308</v>
       </c>
-      <c r="E3" t="n">
-        <v>497</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>232</v>
+        <v>202</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>472</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -519,12 +571,20 @@
       <c r="D4" t="n">
         <v>2360</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>239</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>27</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>3212</v>
       </c>
-      <c r="E5" t="n">
-        <v>474</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
+        <v>448</v>
+      </c>
+      <c r="G5" t="n">
         <v>27</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>26</v>
+      </c>
+      <c r="J5" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -563,12 +639,20 @@
       <c r="D6" t="n">
         <v>2316</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>228</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>27</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +669,20 @@
       <c r="D7" t="n">
         <v>2612</v>
       </c>
-      <c r="E7" t="n">
-        <v>525</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>177</v>
-      </c>
+        <v>370</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +699,12 @@
       <c r="D8" t="n">
         <v>1276</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +721,20 @@
       <c r="D9" t="n">
         <v>1408</v>
       </c>
-      <c r="E9" t="n">
-        <v>367</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>203</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="G9" t="n">
+        <v>31</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +751,12 @@
       <c r="D10" t="n">
         <v>1068</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +773,20 @@
       <c r="D11" t="n">
         <v>1368</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>88</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>31</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +803,27 @@
       <c r="D12" t="n">
         <v>2488</v>
       </c>
-      <c r="E12" t="n">
-        <v>372</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>319</v>
+        <v>273</v>
+      </c>
+      <c r="G12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>698</v>
+      </c>
+      <c r="J12" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +841,20 @@
       <c r="D13" t="n">
         <v>1012</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>136</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>25</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,11 +871,27 @@
       <c r="D14" t="n">
         <v>1004</v>
       </c>
-      <c r="E14" t="n">
-        <v>164</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>142</v>
+        <v>134</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>117</v>
+      </c>
+      <c r="J14" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -761,11 +909,27 @@
       <c r="D15" t="n">
         <v>3268</v>
       </c>
-      <c r="E15" t="n">
-        <v>567</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>319</v>
+        <v>1088</v>
+      </c>
+      <c r="G15" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>273</v>
+      </c>
+      <c r="J15" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="16">
@@ -783,11 +947,27 @@
       <c r="D16" t="n">
         <v>1840</v>
       </c>
-      <c r="E16" t="n">
-        <v>378</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>136</v>
+        <v>351</v>
+      </c>
+      <c r="G16" t="n">
+        <v>27</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>109</v>
+      </c>
+      <c r="J16" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -805,11 +985,27 @@
       <c r="D17" t="n">
         <v>6040</v>
       </c>
-      <c r="E17" t="n">
-        <v>654</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>142</v>
+        <v>615</v>
+      </c>
+      <c r="G17" t="n">
+        <v>27</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>115</v>
+      </c>
+      <c r="J17" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -827,11 +1023,27 @@
       <c r="D18" t="n">
         <v>4400</v>
       </c>
-      <c r="E18" t="n">
-        <v>1045</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>136</v>
+        <v>218</v>
+      </c>
+      <c r="G18" t="n">
+        <v>27</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>991</v>
+      </c>
+      <c r="J18" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -849,11 +1061,27 @@
       <c r="D19" t="n">
         <v>1252</v>
       </c>
-      <c r="E19" t="n">
-        <v>195</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>174</v>
+        <v>141</v>
+      </c>
+      <c r="G19" t="n">
+        <v>31</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>164</v>
+      </c>
+      <c r="J19" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="20">
@@ -871,12 +1099,20 @@
       <c r="D20" t="n">
         <v>2920</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>200</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>31</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,11 +1129,27 @@
       <c r="D21" t="n">
         <v>2592</v>
       </c>
-      <c r="E21" t="n">
-        <v>244</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F21" t="n">
+        <v>62</v>
+      </c>
+      <c r="G21" t="n">
         <v>36</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>182</v>
+      </c>
+      <c r="J21" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -915,11 +1167,27 @@
       <c r="D22" t="n">
         <v>1896</v>
       </c>
-      <c r="E22" t="n">
-        <v>305</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F22" t="n">
-        <v>220</v>
+        <v>386</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>255</v>
+      </c>
+      <c r="J22" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
